--- a/demo-data/Product_Master.xlsx
+++ b/demo-data/Product_Master.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Price Book" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inventory" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Book" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -392,7 +392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.25" customWidth="1" min="1" max="1"/>
@@ -475,7 +475,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Oncavax IV 100mg Vial</t>
+          <t>Product Alpha</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Oncavax IV 500mg Vial</t>
+          <t>Product Beta</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Rheumera Biosimilar Pen</t>
+          <t>Product Gamma</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Cardiovex 50mg Tablet Pack</t>
+          <t>Product Delta</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Lysomab Rare Disease Kit</t>
+          <t>Product Epsilon</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Companion Diagnostic Panel</t>
+          <t>Product Zeta</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Thrombex Hospital Pack</t>
+          <t>Product Eta</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Dermava Biosimilar Syringe</t>
+          <t>Product Theta</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Tumorex Oral 28-Day Pack</t>
+          <t>Product Iota</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Nervomab Infusion Kit</t>
+          <t>Product Kappa</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>GeneMap Companion Panel</t>
+          <t>Product Lambda</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Patient Access Program</t>
+          <t>Product Mu</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Patient Start Program</t>
+          <t>Product Nu</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Formulary Access Rebate</t>
+          <t>Product Xi</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
